--- a/01_INPUTS/ACCIONES COMERCIALES/2026-08/ORBIT_Acciones_Comerciales_Agosto_2026.xlsx
+++ b/01_INPUTS/ACCIONES COMERCIALES/2026-08/ORBIT_Acciones_Comerciales_Agosto_2026.xlsx
@@ -91,18 +91,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <bottom style="thin">
         <color rgb="FFD8DCE3"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +169,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -629,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1174,39 +1186,76 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>AGO26-PETIT</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Petit Mayoristas</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Acciones por volumen</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>Mayorista</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Volumen</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Activa</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>VDA y Spirits &gt;50 cajas; Espumantes desde 10 cajas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Tradicionales no compradores</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Caja mixta 3+3</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Caja mixta</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>Especiales</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>15% en caja mixta de 6 botellas: 3 de una marca y 3 de otra distinta, entre las 10 marcas elegibles. Solo para clientes del canal Tradicional que en agosto no compraron ninguna de esas marcas (pertenencia al mes por FechaComprobante).</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1346,7 +1395,7 @@
           <t>1 a 9 cajas · 4%</t>
         </is>
       </c>
-      <c r="J5" s="14" t="str"/>
+      <c r="J5" s="14" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -1432,7 +1481,7 @@
           <t>20 cajas o más · 8%</t>
         </is>
       </c>
-      <c r="J7" s="14" t="str"/>
+      <c r="J7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -1474,7 +1523,7 @@
           <t>0 a 3 cajas · 4%</t>
         </is>
       </c>
-      <c r="J8" s="15" t="str"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -1514,7 +1563,7 @@
           <t>4 cajas o más · 8%</t>
         </is>
       </c>
-      <c r="J9" s="14" t="str"/>
+      <c r="J9" s="14" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -1556,7 +1605,7 @@
           <t>0 a 3 cajas · 6%</t>
         </is>
       </c>
-      <c r="J10" s="15" t="str"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -1596,7 +1645,7 @@
           <t>4 cajas o más · 8%</t>
         </is>
       </c>
-      <c r="J11" s="14" t="str"/>
+      <c r="J11" s="14" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -1638,7 +1687,7 @@
           <t>1 a 9 cajas · 6%</t>
         </is>
       </c>
-      <c r="J12" s="15" t="str"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -1724,7 +1773,7 @@
           <t>20 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J14" s="15" t="str"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -1766,7 +1815,7 @@
           <t>0 a 3 cajas · 6%</t>
         </is>
       </c>
-      <c r="J15" s="14" t="str"/>
+      <c r="J15" s="14" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -1806,7 +1855,7 @@
           <t>4 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J16" s="15" t="str"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
@@ -1848,7 +1897,7 @@
           <t>0 a 3 cajas · 8%</t>
         </is>
       </c>
-      <c r="J17" s="14" t="str"/>
+      <c r="J17" s="14" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -1888,7 +1937,7 @@
           <t>4 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J18" s="15" t="str"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
@@ -1928,7 +1977,7 @@
           <t>1 caja o más · 10%</t>
         </is>
       </c>
-      <c r="J19" s="14" t="str"/>
+      <c r="J19" s="14" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -1968,7 +2017,7 @@
           <t>1 caja o más · 10%</t>
         </is>
       </c>
-      <c r="J20" s="15" t="str"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
@@ -2008,7 +2057,7 @@
           <t>1 caja o más · 10%</t>
         </is>
       </c>
-      <c r="J21" s="14" t="str"/>
+      <c r="J21" s="14" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -2050,7 +2099,7 @@
           <t>1 a 9 cajas · 8%</t>
         </is>
       </c>
-      <c r="J22" s="15" t="str"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
@@ -2136,7 +2185,7 @@
           <t>20 cajas o más · 12%</t>
         </is>
       </c>
-      <c r="J24" s="15" t="str"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
@@ -2178,7 +2227,7 @@
           <t>0 a 3 cajas · 8%</t>
         </is>
       </c>
-      <c r="J25" s="14" t="str"/>
+      <c r="J25" s="14" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -2218,7 +2267,7 @@
           <t>4 cajas o más · 12%</t>
         </is>
       </c>
-      <c r="J26" s="15" t="str"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
@@ -2260,7 +2309,7 @@
           <t>0 a 3 cajas · 10%</t>
         </is>
       </c>
-      <c r="J27" s="14" t="str"/>
+      <c r="J27" s="14" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -2300,7 +2349,7 @@
           <t>4 cajas o más · 12%</t>
         </is>
       </c>
-      <c r="J28" s="15" t="str"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
@@ -2342,7 +2391,7 @@
           <t>1 a 9 cajas · 6%</t>
         </is>
       </c>
-      <c r="J29" s="14" t="str"/>
+      <c r="J29" s="14" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -2428,7 +2477,7 @@
           <t>20 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J31" s="14" t="str"/>
+      <c r="J31" s="14" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -2470,7 +2519,7 @@
           <t>0 a 3 cajas · 6%</t>
         </is>
       </c>
-      <c r="J32" s="15" t="str"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
@@ -2510,7 +2559,7 @@
           <t>4 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J33" s="14" t="str"/>
+      <c r="J33" s="14" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -2552,7 +2601,7 @@
           <t>0 a 3 cajas · 8%</t>
         </is>
       </c>
-      <c r="J34" s="15" t="str"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
@@ -2592,7 +2641,7 @@
           <t>4 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J35" s="14" t="str"/>
+      <c r="J35" s="14" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
@@ -2632,7 +2681,7 @@
           <t>1 caja o más · 4%</t>
         </is>
       </c>
-      <c r="J36" s="15" t="str"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -2672,7 +2721,7 @@
           <t>1 pack o más · 7%</t>
         </is>
       </c>
-      <c r="J37" s="14" t="str"/>
+      <c r="J37" s="14" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -2712,7 +2761,7 @@
           <t>Gordon’s Tonic / Antares lata: 1 pack o más · 5%</t>
         </is>
       </c>
-      <c r="J38" s="15" t="str"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
@@ -2752,7 +2801,7 @@
           <t>Smirnoff BC: 1 pack o más · 15%</t>
         </is>
       </c>
-      <c r="J39" s="14" t="str"/>
+      <c r="J39" s="14" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -2792,7 +2841,7 @@
           <t>1 pack o más · 15%</t>
         </is>
       </c>
-      <c r="J40" s="15" t="str"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
@@ -2832,7 +2881,7 @@
           <t>1 caja o más · 5%</t>
         </is>
       </c>
-      <c r="J41" s="14" t="str"/>
+      <c r="J41" s="14" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
@@ -2874,7 +2923,7 @@
           <t>3 unidades · 18%</t>
         </is>
       </c>
-      <c r="J42" s="15" t="str"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
@@ -3000,7 +3049,7 @@
           <t>VDA · 10% sin mínimo y sin topes</t>
         </is>
       </c>
-      <c r="J45" s="14" t="str"/>
+      <c r="J45" s="14" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -3040,7 +3089,7 @@
           <t>Familia Gordon’s / Smirnoff · 8% sin mínimo y sin topes</t>
         </is>
       </c>
-      <c r="J46" s="15" t="str"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
@@ -3080,7 +3129,7 @@
           <t>Espumantes Suter / San Telmo / Dadá · 8% sin mínimo y sin topes</t>
         </is>
       </c>
-      <c r="J47" s="14" t="str"/>
+      <c r="J47" s="14" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
@@ -3215,46 +3264,92 @@
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>AGO26-PETIT</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>Petit Mayoristas</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>Petit Mayoristas</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>caja</t>
         </is>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="26" t="n">
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>descuento</t>
         </is>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="I51" s="14" t="inlineStr">
         <is>
           <t>10 cajas o más · 10%</t>
         </is>
       </c>
-      <c r="J51" s="16" t="inlineStr">
+      <c r="J51" s="14" t="inlineStr">
         <is>
           <t>Aplica a espumantes Suter / San Telmo / Dadá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Tradicional</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>Tradicional | Almacenes | Kioscos</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>botella</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H52" s="28" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="I52" s="28" t="inlineStr">
+        <is>
+          <t>Caja mixta de 6 botellas · 3 + 3 de dos marcas distintas · 15%</t>
+        </is>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>Elegibles: clientes Tradicionales sin compra de ninguna de las 10 marcas durante agosto (FechaComprobante, ImporteNetoItem &gt; 0). La caja debe llevar 3 botellas de una marca y 3 de otra diferente: 6 de una sola marca no califica.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3399,7 +3494,7 @@
           <t>Resolver SKU desde maestro</t>
         </is>
       </c>
-      <c r="E7" s="14" t="str"/>
+      <c r="E7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -3422,7 +3517,7 @@
           <t>Resolver SKU desde maestro</t>
         </is>
       </c>
-      <c r="E8" s="15" t="str"/>
+      <c r="E8" s="15" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -3445,7 +3540,7 @@
           <t>Resolver SKU desde maestro</t>
         </is>
       </c>
-      <c r="E9" s="14" t="str"/>
+      <c r="E9" s="14" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -3468,7 +3563,7 @@
           <t>Resolver SKU/marcas desde maestro</t>
         </is>
       </c>
-      <c r="E10" s="15" t="str"/>
+      <c r="E10" s="15" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -3491,7 +3586,7 @@
           <t>Resolver SKU/marcas desde maestro</t>
         </is>
       </c>
-      <c r="E11" s="14" t="str"/>
+      <c r="E11" s="14" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -3514,7 +3609,7 @@
           <t>Resolver SKU desde maestro</t>
         </is>
       </c>
-      <c r="E12" s="15" t="str"/>
+      <c r="E12" s="15" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -3537,7 +3632,7 @@
           <t>Resolver SKU desde maestro</t>
         </is>
       </c>
-      <c r="E13" s="14" t="str"/>
+      <c r="E13" s="14" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -3560,7 +3655,7 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="str"/>
+      <c r="E14" s="15" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -3610,7 +3705,7 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="str"/>
+      <c r="E16" s="15" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
@@ -3633,7 +3728,7 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="E17" s="14" t="str"/>
+      <c r="E17" s="14" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -3656,7 +3751,7 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="E18" s="15" t="str"/>
+      <c r="E18" s="15" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
@@ -3720,12 +3815,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>producto/línea</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Alma Mora Low</t>
+          <t>74827 — Alma Mora Blanco Dulce Low 6x750</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -3735,7 +3830,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Lista principal de la tabla.</t>
+          <t>SKU explicito (antes: entrada generica “Alma Mora Low”). ERP: ALMA MORA BLANCO DULCE LOW 6X750, linea comercial Alma Mora, vigente.</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3842,12 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>producto/línea</t>
+          <t>sku</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Alaris Dulce Cosecha Tinto</t>
+          <t>74887 — Alma Mora Malbec Dulce Low 6x750</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -3762,7 +3857,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Lista principal de la tabla.</t>
+          <t>SKU explicito (antes: entrada generica “Alma Mora Low”). ERP: ALMA MORA MALBEC DULCE LOW 6X750, linea comercial Alma Mora, en proceso de alta en el maestro.</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3874,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Sidra Dadá</t>
+          <t>Alaris Dulce Cosecha Tinto</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -3806,7 +3901,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>NC lata</t>
+          <t>Sidra Dadá</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -3833,7 +3928,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Don David Red Blend</t>
+          <t>NC lata</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
@@ -3860,7 +3955,7 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Blend de Extremos Pinot Noir</t>
+          <t>Don David Red Blend</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -3887,7 +3982,7 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Dadá Extra Brut</t>
+          <t>Blend de Extremos Pinot Noir</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
@@ -3914,7 +4009,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Espumante Medalla</t>
+          <t>Dadá Extra Brut</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
@@ -3931,17 +4026,17 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>AGO26-5X1</t>
+          <t>AGO26-INNOV</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>familia</t>
+          <t>producto/línea</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Smirnoff</t>
+          <t>Espumante Medalla</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -3951,7 +4046,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Solo canales elegibles.</t>
+          <t>Lista principal de la tabla.</t>
         </is>
       </c>
     </row>
@@ -3968,7 +4063,7 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Gordon’s</t>
+          <t>Smirnoff</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -3985,7 +4080,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>AGO26-PLAN-AS</t>
+          <t>AGO26-5X1</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -3995,15 +4090,19 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>VDA</t>
+          <t>Gordon’s</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="str"/>
+          <t>Incluido</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Solo canales elegibles.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -4018,15 +4117,15 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Gordon’s</t>
+          <t>VDA</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="str"/>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
@@ -4041,7 +4140,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Smirnoff</t>
+          <t>Gordon’s</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -4049,7 +4148,7 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="E33" s="14" t="str"/>
+      <c r="E33" s="14" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -4059,12 +4158,12 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>marca</t>
+          <t>familia</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Suter</t>
+          <t>Smirnoff</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -4072,7 +4171,7 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="E34" s="15" t="str"/>
+      <c r="E34" s="15" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
@@ -4087,7 +4186,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Suter</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -4095,7 +4194,7 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="E35" s="14" t="str"/>
+      <c r="E35" s="14" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
@@ -4110,7 +4209,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Dadá espumantes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -4118,7 +4217,7 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="E36" s="15" t="str"/>
+      <c r="E36" s="15" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -4128,47 +4227,47 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>línea</t>
+          <t>marca</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>Resto de SKU elegible</t>
+          <t>Dadá espumantes</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Aplicar exclusiones.</t>
-        </is>
-      </c>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>AGO26-PETIT</t>
+          <t>AGO26-PLAN-AS</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>familia</t>
+          <t>línea</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>VDA</t>
+          <t>Resto de SKU elegible</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>12% / 15% retiro depósito</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="str"/>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Aplicar exclusiones.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
@@ -4183,7 +4282,7 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>Gordon’s</t>
+          <t>VDA</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -4191,7 +4290,7 @@
           <t>12% / 15% retiro depósito</t>
         </is>
       </c>
-      <c r="E39" s="14" t="str"/>
+      <c r="E39" s="14" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -4206,38 +4305,331 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
+          <t>Gordon’s</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>12% / 15% retiro depósito</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-PETIT</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>familia</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
           <t>Smirnoff</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>12% / 15% retiro depósito</t>
         </is>
       </c>
-      <c r="E40" s="15" t="str"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="E41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>AGO26-PETIT</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>marca</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Suter / San Telmo / Dadá espumantes</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="E41" s="16" t="str"/>
+      <c r="E42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Alma Mora</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Alaris</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Finca Las Moras</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Dadá</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Los Árboles</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Trapiche Reserva</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Don David</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Smirnoff botella</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Frizze</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>AGO26-TRAD-NC</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>marca</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>Gordon's</t>
+        </is>
+      </c>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>Elegible para la caja mixta 3+3 · 15%</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>Comprar esta marca durante agosto deja al cliente fuera de la accion (deja de ser no comprador).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
